--- a/artfynd/A 35141-2023 artfynd.xlsx
+++ b/artfynd/A 35141-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35141-2023 artfynd.xlsx
+++ b/artfynd/A 35141-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112606884</v>
+        <v>112610484</v>
       </c>
       <c r="B5" t="n">
-        <v>77856</v>
+        <v>77954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409607</v>
+        <v>409743</v>
       </c>
       <c r="R5" t="n">
-        <v>6852356</v>
+        <v>6852316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1130,220 +1130,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112610484</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77954</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>967</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Varglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Letharia vulpina</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Dyvelblästan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>409743</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6852316</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606883</v>
-      </c>
-      <c r="B7" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Dyvelblästan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>409608</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6852353</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35141-2023 artfynd.xlsx
+++ b/artfynd/A 35141-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610484</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>